--- a/datosSesionesSin0PValues.xlsx
+++ b/datosSesionesSin0PValues.xlsx
@@ -533,13 +533,13 @@
         <v>0.009840879047869219</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02728988434119468</v>
+        <v>0.02866345894629199</v>
       </c>
       <c r="E2" t="n">
         <v>0.1115951739199692</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8722474807254867</v>
+        <v>0.004223405601919666</v>
       </c>
       <c r="G2" t="n">
         <v>3.515093346767557e-05</v>
@@ -594,13 +594,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1420106966949841</v>
+        <v>0.1402137587551774</v>
       </c>
       <c r="E3" t="n">
         <v>0.06015332062201711</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5362687851499361</v>
+        <v>0.1200329626494199</v>
       </c>
       <c r="G3" t="n">
         <v>0.01811410210996146</v>
@@ -649,58 +649,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02728988434119468</v>
+        <v>0.02866345894629199</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1420106966949841</v>
+        <v>0.1402137587551774</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5060043549175807</v>
+        <v>0.5204570879149462</v>
       </c>
       <c r="F4" t="n">
-        <v>0.384842479431053</v>
+        <v>1.848384577923778e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>1.223201732010748e-06</v>
+        <v>1.488868426316997e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>3.841713248304901e-05</v>
+        <v>4.640815038992619e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.260157364257286e-07</v>
+        <v>8.985125529586274e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.821073705505234e-10</v>
+        <v>3.327163073292744e-10</v>
       </c>
       <c r="K4" t="n">
-        <v>8.198846044608673e-08</v>
+        <v>1.363223039785244e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001367261978649868</v>
+        <v>0.0001190993300155387</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001519908882607607</v>
+        <v>0.001549659843968657</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01660656006999289</v>
+        <v>0.0167262048312136</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002689434821094675</v>
+        <v>0.0002798967890159379</v>
       </c>
       <c r="P4" t="n">
-        <v>1.222800699690331e-18</v>
+        <v>3.031402473617326e-18</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.439247266102923e-12</v>
+        <v>1.070252458302204e-11</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04884341789349898</v>
+        <v>0.04532577214542011</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01887686024088765</v>
+        <v>0.01722353934194692</v>
       </c>
     </row>
     <row r="5">
@@ -716,13 +716,13 @@
         <v>0.06015332062201711</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5060043549175807</v>
+        <v>0.5204570879149462</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4518205807271502</v>
+        <v>0.7664396263664635</v>
       </c>
       <c r="G5" t="n">
         <v>0.0003117119310260491</v>
@@ -771,58 +771,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8722474807254867</v>
+        <v>0.004223405601919666</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5362687851499361</v>
+        <v>0.1200329626494199</v>
       </c>
       <c r="D6" t="n">
-        <v>0.384842479431053</v>
+        <v>1.848384577923778e-10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4518205807271502</v>
+        <v>0.7664396263664635</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8758399446091805</v>
+        <v>4.010246331847915e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8530235118750105</v>
+        <v>1.257115697223098e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2125436564674985</v>
+        <v>1.267890094520871e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4333679892304945</v>
+        <v>1.798761077594842e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2547422099098134</v>
+        <v>3.807558423502223e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1689911689382142</v>
+        <v>0.01502598837058524</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4023624719237942</v>
+        <v>0.0001020324235286631</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4728742040233708</v>
+        <v>0.002846676341073513</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4342741223849984</v>
+        <v>1.664567711554432e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9845786909095884</v>
+        <v>6.029254162041874e-13</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5281452060812455</v>
+        <v>3.336986925972882e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05562346164713924</v>
+        <v>0.003223611858810692</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05440567142695998</v>
+        <v>0.00284646823333454</v>
       </c>
     </row>
     <row r="7">
@@ -838,13 +838,13 @@
         <v>0.01811410210996146</v>
       </c>
       <c r="D7" t="n">
-        <v>1.223201732010748e-06</v>
+        <v>1.488868426316997e-06</v>
       </c>
       <c r="E7" t="n">
         <v>0.0003117119310260491</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8758399446091805</v>
+        <v>4.010246331847915e-07</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.01382015986014685</v>
       </c>
       <c r="D8" t="n">
-        <v>3.841713248304901e-05</v>
+        <v>4.640815038992619e-05</v>
       </c>
       <c r="E8" t="n">
         <v>7.267538095489634e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8530235118750105</v>
+        <v>1.257115697223098e-05</v>
       </c>
       <c r="G8" t="n">
         <v>4.983382107178926e-42</v>
@@ -960,13 +960,13 @@
         <v>0.3084909682282586</v>
       </c>
       <c r="D9" t="n">
-        <v>9.260157364257286e-07</v>
+        <v>8.985125529586274e-07</v>
       </c>
       <c r="E9" t="n">
         <v>0.3461375640709028</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2125436564674985</v>
+        <v>1.267890094520871e-06</v>
       </c>
       <c r="G9" t="n">
         <v>3.459962897552534e-09</v>
@@ -1021,13 +1021,13 @@
         <v>0.01763129093367518</v>
       </c>
       <c r="D10" t="n">
-        <v>1.821073705505234e-10</v>
+        <v>3.327163073292744e-10</v>
       </c>
       <c r="E10" t="n">
         <v>0.008897941078289635</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4333679892304945</v>
+        <v>1.798761077594842e-08</v>
       </c>
       <c r="G10" t="n">
         <v>2.986342970699734e-23</v>
@@ -1082,13 +1082,13 @@
         <v>0.01870246979315746</v>
       </c>
       <c r="D11" t="n">
-        <v>8.198846044608673e-08</v>
+        <v>1.363223039785244e-07</v>
       </c>
       <c r="E11" t="n">
         <v>0.01099073551830001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2547422099098134</v>
+        <v>3.807558423502223e-07</v>
       </c>
       <c r="G11" t="n">
         <v>3.624698535213484e-22</v>
@@ -1143,13 +1143,13 @@
         <v>0.6654650694685547</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001367261978649868</v>
+        <v>0.0001190993300155387</v>
       </c>
       <c r="E12" t="n">
         <v>0.506571819157394</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1689911689382142</v>
+        <v>0.01502598837058524</v>
       </c>
       <c r="G12" t="n">
         <v>0.1712454830642173</v>
@@ -1204,13 +1204,13 @@
         <v>0.04342575981657415</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001519908882607607</v>
+        <v>0.001549659843968657</v>
       </c>
       <c r="E13" t="n">
         <v>0.0001303945547158257</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4023624719237942</v>
+        <v>0.0001020324235286631</v>
       </c>
       <c r="G13" t="n">
         <v>3.887147421430556e-31</v>
@@ -1265,13 +1265,13 @@
         <v>0.03269079578093229</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01660656006999289</v>
+        <v>0.0167262048312136</v>
       </c>
       <c r="E14" t="n">
         <v>3.680986488175263e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4728742040233708</v>
+        <v>0.002846676341073513</v>
       </c>
       <c r="G14" t="n">
         <v>1.834599425246016e-23</v>
@@ -1326,13 +1326,13 @@
         <v>0.3282511144196319</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002689434821094675</v>
+        <v>0.0002798967890159379</v>
       </c>
       <c r="E15" t="n">
         <v>0.4385639521559522</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4342741223849984</v>
+        <v>1.664567711554432e-05</v>
       </c>
       <c r="G15" t="n">
         <v>4.536675247822425e-10</v>
@@ -1387,13 +1387,13 @@
         <v>0.01949715369309717</v>
       </c>
       <c r="D16" t="n">
-        <v>1.222800699690331e-18</v>
+        <v>3.031402473617326e-18</v>
       </c>
       <c r="E16" t="n">
         <v>0.1344226703949794</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9845786909095884</v>
+        <v>6.029254162041874e-13</v>
       </c>
       <c r="G16" t="n">
         <v>1.119963982812957e-13</v>
@@ -1448,13 +1448,13 @@
         <v>0.02939609122673541</v>
       </c>
       <c r="D17" t="n">
-        <v>8.439247266102923e-12</v>
+        <v>1.070252458302204e-11</v>
       </c>
       <c r="E17" t="n">
         <v>0.0362609903867257</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5281452060812455</v>
+        <v>3.336986925972882e-10</v>
       </c>
       <c r="G17" t="n">
         <v>8.498141004449297e-15</v>
@@ -1509,13 +1509,13 @@
         <v>0.176081161108752</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04884341789349898</v>
+        <v>0.04532577214542011</v>
       </c>
       <c r="E18" t="n">
         <v>0.03130001230091634</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05562346164713924</v>
+        <v>0.003223611858810692</v>
       </c>
       <c r="G18" t="n">
         <v>0.4004567181962336</v>
@@ -1570,13 +1570,13 @@
         <v>0.1354530352931255</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01887686024088765</v>
+        <v>0.01722353934194692</v>
       </c>
       <c r="E19" t="n">
         <v>0.1420855589304852</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05440567142695998</v>
+        <v>0.00284646823333454</v>
       </c>
       <c r="G19" t="n">
         <v>0.5714183821075677</v>

--- a/datosSesionesSin0PValues.xlsx
+++ b/datosSesionesSin0PValues.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -580,6 +590,12 @@
       <c r="S2" t="n">
         <v>0.1293799245793948</v>
       </c>
+      <c r="T2" t="n">
+        <v>0.4181327902642565</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.4181327902642556</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -641,6 +657,12 @@
       <c r="S3" t="n">
         <v>0.1354530352931255</v>
       </c>
+      <c r="T3" t="n">
+        <v>0.4406010049683858</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.4406010049683823</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -702,6 +724,12 @@
       <c r="S4" t="n">
         <v>0.01722353934194692</v>
       </c>
+      <c r="T4" t="n">
+        <v>0.1239074052113945</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1239074052113941</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -763,6 +791,12 @@
       <c r="S5" t="n">
         <v>0.1420855589304852</v>
       </c>
+      <c r="T5" t="n">
+        <v>0.03216030593055469</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.03216030593055422</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -824,6 +858,12 @@
       <c r="S6" t="n">
         <v>0.00284646823333454</v>
       </c>
+      <c r="T6" t="n">
+        <v>0.09268392067639269</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.09268392067639269</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -885,6 +925,12 @@
       <c r="S7" t="n">
         <v>0.5714183821075677</v>
       </c>
+      <c r="T7" t="n">
+        <v>0.591195989260267</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5911959892602644</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -946,6 +992,12 @@
       <c r="S8" t="n">
         <v>0.2748305863001195</v>
       </c>
+      <c r="T8" t="n">
+        <v>0.0450286377682303</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.04502863776822989</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1007,6 +1059,12 @@
       <c r="S9" t="n">
         <v>0.148823170774678</v>
       </c>
+      <c r="T9" t="n">
+        <v>6.037479939338889e-07</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6.037479939339032e-07</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1068,6 +1126,12 @@
       <c r="S10" t="n">
         <v>0.7233652316842358</v>
       </c>
+      <c r="T10" t="n">
+        <v>0.4051832618359465</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.4051832618359453</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1129,6 +1193,12 @@
       <c r="S11" t="n">
         <v>0.556600234427872</v>
       </c>
+      <c r="T11" t="n">
+        <v>0.09312112902437641</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.09312112902437561</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1190,6 +1260,12 @@
       <c r="S12" t="n">
         <v>1.497005040742491e-05</v>
       </c>
+      <c r="T12" t="n">
+        <v>0.0003857343439993188</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.000385734343999313</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1251,6 +1327,12 @@
       <c r="S13" t="n">
         <v>0.2377638138454037</v>
       </c>
+      <c r="T13" t="n">
+        <v>0.8074765853930048</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.8074765853930004</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1312,6 +1394,12 @@
       <c r="S14" t="n">
         <v>0.1690401392173643</v>
       </c>
+      <c r="T14" t="n">
+        <v>0.04993944285496145</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.04993944285496082</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1373,6 +1461,12 @@
       <c r="S15" t="n">
         <v>0.7691745604299897</v>
       </c>
+      <c r="T15" t="n">
+        <v>0.0001137536074769554</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0001137536074769584</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1434,6 +1528,12 @@
       <c r="S16" t="n">
         <v>0.1618089313082533</v>
       </c>
+      <c r="T16" t="n">
+        <v>0.8218484457677869</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.8218484457677869</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1495,6 +1595,12 @@
       <c r="S17" t="n">
         <v>0.972818317694776</v>
       </c>
+      <c r="T17" t="n">
+        <v>0.5195736536461724</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5195736536461724</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1556,6 +1662,12 @@
       <c r="S18" t="n">
         <v>6.451576868915925e-32</v>
       </c>
+      <c r="T18" t="n">
+        <v>0.05905743188866704</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.05905743188866537</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1615,6 +1727,146 @@
         <v>6.451576868915925e-32</v>
       </c>
       <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.004434351967488126</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.004434351967487995</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4181327902642565</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4406010049683858</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1239074052113945</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.03216030593055469</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.09268392067639269</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.591195989260267</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0450286377682303</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.037479939338889e-07</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4051832618359465</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.09312112902437641</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0003857343439993188</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8074765853930048</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.04993944285496145</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0001137536074769554</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.8218484457677869</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5195736536461724</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.05905743188866704</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.004434351967488126</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.4181327902642556</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4406010049683823</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1239074052113941</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.03216030593055422</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.09268392067639269</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5911959892602644</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.04502863776822989</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.037479939339032e-07</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4051832618359453</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.09312112902437561</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.000385734343999313</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8074765853930004</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.04993944285496082</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0001137536074769584</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.8218484457677869</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.5195736536461724</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.05905743188866537</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.004434351967487995</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
